--- a/Pet_project_excel.xlsx
+++ b/Pet_project_excel.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6970" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6970" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="DataSet" sheetId="1" r:id="rId1"/>
@@ -9139,6 +9139,72 @@
     <cellStyle name="Процентный" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="63">
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <name val="Times New Roman"/>
@@ -9412,72 +9478,6 @@
         <sz val="12"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -9509,38 +9509,7 @@
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
-    <c:title>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -10180,11 +10149,11 @@
         </c:dLbls>
         <c:gapWidth val="164"/>
         <c:overlap val="-22"/>
-        <c:axId val="378587072"/>
-        <c:axId val="378588640"/>
+        <c:axId val="378816480"/>
+        <c:axId val="378817264"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="378587072"/>
+        <c:axId val="378816480"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10227,7 +10196,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378588640"/>
+        <c:crossAx val="378817264"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10235,7 +10204,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="378588640"/>
+        <c:axId val="378817264"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10272,7 +10241,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378587072"/>
+        <c:crossAx val="378816480"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10382,38 +10351,7 @@
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
-    <c:title>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="0" normalizeH="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -10542,11 +10480,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="247"/>
-        <c:axId val="378584720"/>
-        <c:axId val="378589816"/>
+        <c:axId val="378817656"/>
+        <c:axId val="378818832"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="378584720"/>
+        <c:axId val="378817656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10603,7 +10541,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378589816"/>
+        <c:crossAx val="378818832"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -10611,7 +10549,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="378589816"/>
+        <c:axId val="378818832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -10662,7 +10600,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378584720"/>
+        <c:crossAx val="378817656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -10684,38 +10622,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -10756,7 +10662,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -10782,37 +10687,7 @@
     <c:fmtId val="5"/>
   </c:pivotSource>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -11423,12 +11298,12 @@
         </c:dLbls>
         <c:gapWidth val="150"/>
         <c:shape val="box"/>
-        <c:axId val="378589032"/>
-        <c:axId val="378588248"/>
+        <c:axId val="378820008"/>
+        <c:axId val="378820400"/>
         <c:axId val="0"/>
       </c:bar3DChart>
       <c:catAx>
-        <c:axId val="378589032"/>
+        <c:axId val="378820008"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11471,7 +11346,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378588248"/>
+        <c:crossAx val="378820400"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11479,7 +11354,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="378588248"/>
+        <c:axId val="378820400"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11530,7 +11405,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378589032"/>
+        <c:crossAx val="378820008"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11544,6 +11419,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="r"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11639,37 +11515,7 @@
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1600" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="none" spc="50" normalizeH="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mj-lt"/>
-              <a:ea typeface="+mj-ea"/>
-              <a:cs typeface="+mj-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -11695,6 +11541,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -11732,7 +11579,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -11809,6 +11658,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -11903,11 +11753,11 @@
         </c:dLbls>
         <c:gapWidth val="80"/>
         <c:overlap val="25"/>
-        <c:axId val="378583544"/>
-        <c:axId val="378590600"/>
+        <c:axId val="378821968"/>
+        <c:axId val="327755800"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="378583544"/>
+        <c:axId val="378821968"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11950,7 +11800,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378590600"/>
+        <c:crossAx val="327755800"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11958,7 +11808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="378590600"/>
+        <c:axId val="327755800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12009,7 +11859,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="378583544"/>
+        <c:crossAx val="378821968"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12021,37 +11871,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -12092,7 +11911,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -12118,37 +11936,7 @@
     <c:fmtId val="3"/>
   </c:pivotSource>
   <c:chart>
-    <c:title>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
+    <c:autoTitleDeleted val="1"/>
     <c:pivotFmts>
       <c:pivotFmt>
         <c:idx val="0"/>
@@ -12179,6 +11967,7 @@
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -12213,7 +12002,9 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -12292,6 +12083,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -12367,11 +12159,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="65"/>
-        <c:axId val="325317704"/>
-        <c:axId val="325318096"/>
+        <c:axId val="327756584"/>
+        <c:axId val="327759720"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="325317704"/>
+        <c:axId val="327756584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12414,7 +12206,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="325318096"/>
+        <c:crossAx val="327759720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12422,7 +12214,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="325318096"/>
+        <c:axId val="327759720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12485,7 +12277,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="325317704"/>
+        <c:crossAx val="327756584"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12497,42 +12289,6 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:solidFill>
-          <a:schemeClr val="lt1">
-            <a:lumMod val="95000"/>
-            <a:alpha val="39000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1">
-                  <a:lumMod val="75000"/>
-                  <a:lumOff val="25000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
@@ -12589,7 +12345,6 @@
         <c14:dropZoneFilter val="1"/>
         <c14:dropZoneCategories val="1"/>
         <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
         <c14:dropZonesVisible val="1"/>
       </c14:pivotOptions>
     </c:ext>
@@ -15681,15 +15436,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>25400</xdr:colOff>
+      <xdr:colOff>50800</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
-      <xdr:colOff>330200</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>165100</xdr:rowOff>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -31513,22 +31268,22 @@
     <dataField name="Среднее по полю Points" fld="3" subtotal="average" baseField="0" baseItem="49" numFmtId="164"/>
   </dataFields>
   <formats count="13">
-    <format dxfId="12">
+    <format dxfId="24">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="11">
+    <format dxfId="23">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="10">
+    <format dxfId="22">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="9">
+    <format dxfId="21">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="8">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="10">
@@ -31546,22 +31301,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="6">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="17">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="16">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="3">
+    <format dxfId="15">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="14">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="13">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="10">
@@ -31579,7 +31334,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="0">
+    <format dxfId="12">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -31920,19 +31675,19 @@
     <dataField name="Количество по полю Country" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="24">
+    <format dxfId="36">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="35">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="34">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="21">
+    <format dxfId="33">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="20">
+    <format dxfId="32">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="11">
@@ -31951,22 +31706,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="31">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="18">
+    <format dxfId="30">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="17">
+    <format dxfId="29">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="16">
+    <format dxfId="28">
       <pivotArea field="0" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="27">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="26">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="0" count="11">
@@ -31985,7 +31740,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="25">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -32292,7 +32047,7 @@
     <dataField name="Среднее по полю Points" fld="3" subtotal="average" baseField="1" baseItem="1" numFmtId="164"/>
   </dataFields>
   <formats count="14">
-    <format dxfId="38">
+    <format dxfId="50">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="1">
@@ -32301,22 +32056,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="37">
+    <format dxfId="49">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="36">
+    <format dxfId="48">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="35">
+    <format dxfId="47">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="34">
+    <format dxfId="46">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="33">
+    <format dxfId="45">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="32">
+    <format dxfId="44">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="8">
@@ -32332,22 +32087,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="31">
+    <format dxfId="43">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="30">
+    <format dxfId="42">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="29">
+    <format dxfId="41">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="28">
+    <format dxfId="40">
       <pivotArea field="1" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="27">
+    <format dxfId="39">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="26">
+    <format dxfId="38">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="1" count="8">
@@ -32363,7 +32118,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="25">
+    <format dxfId="37">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -33805,19 +33560,19 @@
     <dataField name="Сумма по полю Points" fld="3" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="50">
+    <format dxfId="0">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="49">
+    <format dxfId="1">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="48">
+    <format dxfId="2">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="47">
+    <format dxfId="3">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="46">
+    <format dxfId="4">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="5">
@@ -33830,22 +33585,22 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="45">
+    <format dxfId="5">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="44">
+    <format dxfId="6">
       <pivotArea type="all" dataOnly="0" outline="0" fieldPosition="0"/>
     </format>
-    <format dxfId="43">
+    <format dxfId="7">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="42">
+    <format dxfId="8">
       <pivotArea field="6" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="41">
+    <format dxfId="9">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="40">
+    <format dxfId="10">
       <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
         <references count="1">
           <reference field="6" count="5">
@@ -33858,7 +33613,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="39">
+    <format dxfId="11">
       <pivotArea dataOnly="0" labelOnly="1" grandRow="1" outline="0" fieldPosition="0"/>
     </format>
   </formats>
@@ -34251,7 +34006,7 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <slicer name="Country" cache="Срез_Country" caption="Country" startItem="21" style="SlicerStyleLight2" rowHeight="241300"/>
+  <slicer name="Country" cache="Срез_Country" caption="Country" startItem="3" style="SlicerStyleLight2" rowHeight="241300"/>
   <slicer name="Year" cache="Срез_Year" caption="Year" rowHeight="241300"/>
   <slicer name="Type" cache="Срез_Type" caption="Type" style="SlicerStyleOther1" rowHeight="241300"/>
 </slicers>
